--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="194">
   <si>
     <t>DetailsDBData</t>
   </si>
@@ -601,6 +601,9 @@
   </si>
   <si>
     <t>62703</t>
+  </si>
+  <si>
+    <t>ISP</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1618,7 @@
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
         <v>189</v>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5037" uniqueCount="194">
   <si>
     <t>DetailsDBData</t>
   </si>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5037" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5931" uniqueCount="197">
   <si>
     <t>DetailsDBData</t>
   </si>
@@ -604,6 +604,15 @@
   </si>
   <si>
     <t>ISP</t>
+  </si>
+  <si>
+    <t>Chicago State University</t>
+  </si>
+  <si>
+    <t>9501 S. King Dr.</t>
+  </si>
+  <si>
+    <t>60628</t>
   </si>
 </sst>
 </file>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5931" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6080" uniqueCount="197">
   <si>
     <t>DetailsDBData</t>
   </si>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6080" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7421" uniqueCount="197">
   <si>
     <t>DetailsDBData</t>
   </si>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="4">
       <c r="C4" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="5">
       <c r="C5" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -1627,19 +1627,19 @@
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="G8" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -1673,22 +1673,22 @@
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -1696,19 +1696,19 @@
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1719,19 +1719,19 @@
     </row>
     <row r="12">
       <c r="C12" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1742,22 +1742,22 @@
     </row>
     <row r="13">
       <c r="C13" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1765,19 +1765,19 @@
     </row>
     <row r="14">
       <c r="C14" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -1788,22 +1788,22 @@
     </row>
     <row r="15">
       <c r="C15" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I15" t="s">
         <v>21</v>
@@ -1811,22 +1811,22 @@
     </row>
     <row r="16">
       <c r="C16" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1834,22 +1834,22 @@
     </row>
     <row r="17">
       <c r="C17" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="H17" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1857,22 +1857,22 @@
     </row>
     <row r="18">
       <c r="C18" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="H18" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I18" t="s">
         <v>21</v>
@@ -1880,19 +1880,19 @@
     </row>
     <row r="19">
       <c r="C19" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -1903,22 +1903,22 @@
     </row>
     <row r="20">
       <c r="C20" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="H20" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1926,19 +1926,19 @@
     </row>
     <row r="21">
       <c r="C21" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="F21" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7421" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7570" uniqueCount="197">
   <si>
     <t>DetailsDBData</t>
   </si>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="4">
       <c r="C4" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="5">
       <c r="C5" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -1627,19 +1627,19 @@
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -1673,22 +1673,22 @@
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -1696,19 +1696,19 @@
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1719,19 +1719,19 @@
     </row>
     <row r="12">
       <c r="C12" t="s">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1742,22 +1742,22 @@
     </row>
     <row r="13">
       <c r="C13" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1765,19 +1765,19 @@
     </row>
     <row r="14">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -1788,22 +1788,22 @@
     </row>
     <row r="15">
       <c r="C15" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
         <v>21</v>
@@ -1811,22 +1811,22 @@
     </row>
     <row r="16">
       <c r="C16" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1834,22 +1834,22 @@
     </row>
     <row r="17">
       <c r="C17" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1857,22 +1857,22 @@
     </row>
     <row r="18">
       <c r="C18" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
         <v>21</v>
@@ -1880,19 +1880,19 @@
     </row>
     <row r="19">
       <c r="C19" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -1903,22 +1903,22 @@
     </row>
     <row r="20">
       <c r="C20" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>176</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1926,19 +1926,19 @@
     </row>
     <row r="21">
       <c r="C21" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7570" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8762" uniqueCount="197">
   <si>
     <t>DetailsDBData</t>
   </si>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="4">
       <c r="C4" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="5">
       <c r="C5" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -1627,19 +1627,19 @@
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="G8" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -1673,22 +1673,22 @@
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -1696,19 +1696,19 @@
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1719,19 +1719,19 @@
     </row>
     <row r="12">
       <c r="C12" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1742,22 +1742,22 @@
     </row>
     <row r="13">
       <c r="C13" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1765,19 +1765,19 @@
     </row>
     <row r="14">
       <c r="C14" t="s">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -1788,22 +1788,22 @@
     </row>
     <row r="15">
       <c r="C15" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I15" t="s">
         <v>21</v>
@@ -1811,22 +1811,22 @@
     </row>
     <row r="16">
       <c r="C16" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1834,22 +1834,22 @@
     </row>
     <row r="17">
       <c r="C17" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="H17" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1857,22 +1857,22 @@
     </row>
     <row r="18">
       <c r="C18" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>178</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="H18" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I18" t="s">
         <v>21</v>
@@ -1880,19 +1880,19 @@
     </row>
     <row r="19">
       <c r="C19" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -1903,22 +1903,22 @@
     </row>
     <row r="20">
       <c r="C20" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="H20" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1926,19 +1926,19 @@
     </row>
     <row r="21">
       <c r="C21" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="F21" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8762" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8911" uniqueCount="197">
   <si>
     <t>DetailsDBData</t>
   </si>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8911" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9209" uniqueCount="198">
   <si>
     <t>DetailsDBData</t>
   </si>
@@ -613,6 +613,9 @@
   </si>
   <si>
     <t>60628</t>
+  </si>
+  <si>
+    <t>cgOrg</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1538,7 @@
     </row>
     <row r="4">
       <c r="C4" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -1558,10 +1561,10 @@
     </row>
     <row r="5">
       <c r="C5" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1570,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -1616,7 +1619,7 @@
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -1627,19 +1630,19 @@
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -1673,22 +1676,22 @@
     </row>
     <row r="10">
       <c r="C10" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -1696,19 +1699,19 @@
     </row>
     <row r="11">
       <c r="C11" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1719,19 +1722,19 @@
     </row>
     <row r="12">
       <c r="C12" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1742,22 +1745,22 @@
     </row>
     <row r="13">
       <c r="C13" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
         <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
         <v>21</v>
@@ -1765,19 +1768,19 @@
     </row>
     <row r="14">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -1788,22 +1791,22 @@
     </row>
     <row r="15">
       <c r="C15" t="s">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
         <v>21</v>
@@ -1811,22 +1814,22 @@
     </row>
     <row r="16">
       <c r="C16" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="I16" t="s">
         <v>21</v>
@@ -1834,22 +1837,22 @@
     </row>
     <row r="17">
       <c r="C17" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I17" t="s">
         <v>21</v>
@@ -1857,22 +1860,22 @@
     </row>
     <row r="18">
       <c r="C18" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I18" t="s">
         <v>21</v>
@@ -1880,19 +1883,19 @@
     </row>
     <row r="19">
       <c r="C19" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -1903,22 +1906,22 @@
     </row>
     <row r="20">
       <c r="C20" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>176</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -1926,19 +1929,19 @@
     </row>
     <row r="21">
       <c r="C21" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9209" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9358" uniqueCount="198">
   <si>
     <t>DetailsDBData</t>
   </si>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9358" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9507" uniqueCount="198">
   <si>
     <t>DetailsDBData</t>
   </si>

--- a/Test Data/OutputData.xlsx
+++ b/Test Data/OutputData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9507" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9656" uniqueCount="198">
   <si>
     <t>DetailsDBData</t>
   </si>
